--- a/public/file/Employee Payslip Template.xlsx
+++ b/public/file/Employee Payslip Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91B9BD1-A84B-43CA-9DC2-8F17BF79A2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078D43B1-52FA-4309-A871-C0F4F0E157A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{D8DAC57B-AAFF-4B9B-A183-BE5D1A9458CA}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>Employee Name</t>
   </si>
@@ -190,6 +190,12 @@
   </si>
   <si>
     <t>Recovery</t>
+  </si>
+  <si>
+    <t>Confirmation Date</t>
+  </si>
+  <si>
+    <t>Employee Type</t>
   </si>
 </sst>
 </file>
@@ -597,14 +603,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965DC364-1DD8-4CF7-98AD-204F8F0E04FA}">
-  <dimension ref="A1:BC1"/>
+  <dimension ref="A1:BE1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:57" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -769,6 +775,12 @@
       </c>
       <c r="BC1" s="3" t="s">
         <v>53</v>
+      </c>
+      <c r="BD1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Employee Payslip Template.xlsx
+++ b/public/file/Employee Payslip Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078D43B1-52FA-4309-A871-C0F4F0E157A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF312F5-94D6-4A92-83AF-98186C55F469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{D8DAC57B-AAFF-4B9B-A183-BE5D1A9458CA}"/>
   </bookViews>
@@ -277,7 +277,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -288,6 +288,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -606,8 +607,9 @@
   <dimension ref="A1:BE1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.109375" customWidth="1"/>
+    <col min="56" max="56" width="19.88671875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">

--- a/public/file/Employee Payslip Template.xlsx
+++ b/public/file/Employee Payslip Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TRAX\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF312F5-94D6-4A92-83AF-98186C55F469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0F0209-A626-4C16-803C-D61DFF71ECC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{D8DAC57B-AAFF-4B9B-A183-BE5D1A9458CA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D8DAC57B-AAFF-4B9B-A183-BE5D1A9458CA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Employee Name</t>
   </si>
@@ -196,6 +196,12 @@
   </si>
   <si>
     <t>Employee Type</t>
+  </si>
+  <si>
+    <t>Retail Incentive</t>
+  </si>
+  <si>
+    <t>Sales Incentive</t>
   </si>
 </sst>
 </file>
@@ -604,15 +610,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965DC364-1DD8-4CF7-98AD-204F8F0E04FA}">
-  <dimension ref="A1:BE1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:BG1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="7" max="7" width="15.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" customWidth="1"/>
-    <col min="56" max="56" width="19.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.08984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.08984375" customWidth="1"/>
+    <col min="32" max="33" width="19.90625" customWidth="1"/>
+    <col min="34" max="34" width="17.7265625" customWidth="1"/>
+    <col min="57" max="57" width="19.90625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:59" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -710,78 +718,84 @@
         <v>22</v>
       </c>
       <c r="AG1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AI1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AR1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AS1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AT1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AU1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AV1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AW1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AX1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AY1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="BA1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BB1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BC1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BD1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BE1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BF1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BG1" s="3" t="s">
         <v>56</v>
       </c>
     </row>
